--- a/Tools/Config/Datas/DazeSetting.xlsx
+++ b/Tools/Config/Datas/DazeSetting.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,11 @@
           <t>ParryDazeRatio</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>VacuumSeconds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -556,6 +561,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -623,6 +633,11 @@
           <t>招架失衡倍率</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>谐度破坏后真空秒</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -685,6 +700,11 @@
           <t>成功招架：100*倍率*(1-抗性)。杂兵0.35约3下破</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>锁零；0则运行时默认5</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -724,6 +744,9 @@
       </c>
       <c r="M6" t="n">
         <v>0.35</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -765,6 +788,9 @@
       <c r="M7" t="n">
         <v>0.55</v>
       </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -804,6 +830,9 @@
       </c>
       <c r="M8" t="n">
         <v>0.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
